--- a/week5/programming/HeapSort/Complexity_Chart.xlsx
+++ b/week5/programming/HeapSort/Complexity_Chart.xlsx
@@ -2,31 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Work\UCA\week4\programming\quickSelect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UCA\week5\programming\HeapSort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B246D7CF-BFD7-406E-B3E5-97A48F802714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BE9133-1DA7-4909-836D-0DCACEFFF3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runtime Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Runtime Chart" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Dataset Size (n)</t>
+    <t>Size</t>
   </si>
   <si>
-    <t>Execution Time (ms)</t>
+    <t>Random Avg (ms)</t>
+  </si>
+  <si>
+    <t>Ascending Avg (ms)</t>
+  </si>
+  <si>
+    <t>Descending Avg (ms)</t>
   </si>
 </sst>
 </file>
@@ -36,17 +41,23 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
-      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,8 +69,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,16 +84,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -92,21 +103,21 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -122,7 +133,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
@@ -135,29 +146,60 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-IN"/>
-              <a:t>Quickselect Average Runtime Analysis</a:t>
+              <a:t>Heap Sort Performance</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
+        <c:varyColors val="1"/>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
@@ -165,96 +207,267 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Execution Time (ms)</c:v>
+                  <c:v>Random Avg (ms)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
+            <a:ln w="47625" cap="rnd" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="1F4E79"/>
+                <a:schemeClr val="accent6">
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="1F4E79"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="1F4E79"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Runtime Data'!$A$2:$A$8</c:f>
+              <c:f>'Runtime Data'!$A$2:$A$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4000</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6000</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8000</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10000</c:v>
+                  <c:v>160000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>14000</c:v>
+                  <c:v>320000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Runtime Data'!$B$2:$B$8</c:f>
+              <c:f>'Runtime Data'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.1999999999999999E-2</c:v>
+                  <c:v>15.648999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.8000000000000003E-2</c:v>
+                  <c:v>9.6920000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7E-2</c:v>
+                  <c:v>30.565000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.9000000000000001E-2</c:v>
+                  <c:v>56.064999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.111</c:v>
+                  <c:v>115.896</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.161</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.122</c:v>
+                  <c:v>266.45600000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-704B-4F79-A61B-05F5E4303632}"/>
+              <c16:uniqueId val="{00000000-C553-4838-893A-AC61716E9F89}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Runtime Data'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ascending Avg (ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="47625" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Runtime Data'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>320000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Runtime Data'!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>13.728</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.1940000000000008</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0579999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.337</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>64.048000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93.563000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C553-4838-893A-AC61716E9F89}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Runtime Data'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Descending Avg (ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="47625" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Runtime Data'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>320000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Runtime Data'!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7.7220000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.195</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.999000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29.001999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75.137</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>221.58799999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C553-4838-893A-AC61716E9F89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -266,94 +479,225 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="411030048"/>
-        <c:axId val="341098800"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="411030048"/>
+        <c:axId val="10"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-IN"/>
-                  <a:t>Dataset Size (n)</a:t>
+                  <a:t>Input Size</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="341098800"/>
+        <c:crossAx val="100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="341098800"/>
+        <c:axId val="100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-IN"/>
-                  <a:t>Execution Time (ms)</a:t>
+                  <a:t>Average Execution Time (ms)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.000" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="411030048"/>
+        <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:tint val="75000"/>
+          <a:shade val="95000"/>
+          <a:satMod val="105000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -362,27 +706,515 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="13">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="bg1"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="lt1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1">
+      <a:schemeClr val="dk1"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="lt1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1">
+      <a:schemeClr val="dk1"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:lineWidthScale>5</cs:lineWidthScale>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln cap="rnd">
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1">
+      <a:schemeClr val="dk1"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1" mods="ignoreCSTransforms">
+      <cs:styleClr val="0">
+        <a:shade val="25000"/>
+      </cs:styleClr>
+    </cs:fillRef>
+    <cs:effectRef idx="1">
+      <a:schemeClr val="dk1"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="bg1"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln cap="rnd">
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1" mods="ignoreCSTransforms">
+      <cs:styleClr val="0">
+        <a:tint val="25000"/>
+      </cs:styleClr>
+    </cs:fillRef>
+    <cs:effectRef idx="1">
+      <a:schemeClr val="dk1"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="6480000" cy="3600000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4F8B1B0-0F89-299F-20B8-53DB9ED367B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -399,7 +1231,7 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -414,44 +1246,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -478,32 +1310,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -530,24 +1344,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -559,229 +1355,280 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="B2" s="3">
-        <v>2.1999999999999999E-2</v>
+        <v>15.648999999999999</v>
+      </c>
+      <c r="C2" s="3">
+        <v>13.728</v>
+      </c>
+      <c r="D2" s="3">
+        <v>7.7220000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="B3" s="3">
-        <v>5.8000000000000003E-2</v>
+        <v>9.6920000000000002</v>
+      </c>
+      <c r="C3" s="3">
+        <v>8.1940000000000008</v>
+      </c>
+      <c r="D3" s="3">
+        <v>16.195</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="B4" s="3">
-        <v>4.7E-2</v>
+        <v>30.565000000000001</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.0579999999999998</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10.999000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>8000</v>
+        <v>80000</v>
       </c>
       <c r="B5" s="3">
-        <v>7.9000000000000001E-2</v>
+        <v>56.064999999999998</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16.337</v>
+      </c>
+      <c r="D5" s="3">
+        <v>29.001999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>10000</v>
+        <v>160000</v>
       </c>
       <c r="B6" s="3">
-        <v>0.111</v>
+        <v>115.896</v>
+      </c>
+      <c r="C6" s="3">
+        <v>64.048000000000002</v>
+      </c>
+      <c r="D6" s="3">
+        <v>75.137</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>12000</v>
+        <v>320000</v>
       </c>
       <c r="B7" s="3">
-        <v>0.161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>14000</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.122</v>
+        <v>266.45600000000002</v>
+      </c>
+      <c r="C7" s="3">
+        <v>93.563000000000002</v>
+      </c>
+      <c r="D7" s="3">
+        <v>221.58799999999999</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B246F7-AFAA-4721-A6C4-90B27EEA09A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>